--- a/Assets/_OriginalData/Excel/Define/CommonDefine.xlsx
+++ b/Assets/_OriginalData/Excel/Define/CommonDefine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26145" windowHeight="10440"/>
+    <workbookView windowWidth="22800" windowHeight="11265"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1199,7 +1199,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:4">
